--- a/stock_ux/static/xls/stock_quant.xlsx
+++ b/stock_ux/static/xls/stock_quant.xlsx
@@ -68,7 +68,7 @@
     <t>Importar no aplica el conteo: la lista te muestra la diferencia de cada línea y aplicás cuando terminaste de revisar.</t>
   </si>
   <si>
-    <t>Un producto con Seguimiento de inventario desactivado no puede tener stock. Esas filas se informan una por una para que las corrijas o las saques del archivo.</t>
+    <t>Un producto con "Rastrear inventario" desactivado no puede tener stock. Esas filas se informan una por una para que las corrijas o las saques del archivo.</t>
   </si>
   <si>
     <t>Agregá una columna Paquete o Propietario solo si los usás: también forman parte de lo que identifica una línea de stock.</t>
